--- a/CS02_Nykaa_IPO_analysis.xlsx
+++ b/CS02_Nykaa_IPO_analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Apurvi_Bajpai_FP&amp;A_Portfolio\CS03_NYKAA_IPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25F2CD1-69E7-46CE-9995-1C9BA0913809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC4DCF81-8B7E-448D-A349-A4ECBF32108F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{B47DB39E-2DF8-42DF-AEFA-BAA315624893}"/>
+    <workbookView xWindow="7764" yWindow="0" windowWidth="15372" windowHeight="12336" firstSheet="2" activeTab="3" xr2:uid="{B47DB39E-2DF8-42DF-AEFA-BAA315624893}"/>
   </bookViews>
   <sheets>
     <sheet name="Case Overview" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="161">
   <si>
     <t>Project Information</t>
   </si>
@@ -1105,14 +1105,31 @@
   <si>
     <t>Steady improvement</t>
   </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>IPO Issue Price (2021)</t>
+  </si>
+  <si>
+    <t>Current Share Price (2026)</t>
+  </si>
+  <si>
+    <t>Price Change</t>
+  </si>
+  <si>
+    <t>Market Performance vs Business Performance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
+    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="183" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0"/>
+    <numFmt numFmtId="170" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -1936,7 +1953,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1949,222 +1966,36 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2174,59 +2005,13 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2235,9 +2020,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2266,15 +2048,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2294,481 +2067,772 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="13" fillId="5" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="5" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="5" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="0" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="43" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="5" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="5" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="14" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="5" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="18" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2811,7 +2875,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -2821,7 +2885,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Revenue vs Net Profit Trend</a:t>
             </a:r>
           </a:p>
@@ -2840,7 +2904,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3282,7 +3346,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -3292,7 +3356,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Revenue Growth Trend</a:t>
             </a:r>
           </a:p>
@@ -3311,7 +3375,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3732,7 +3796,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -3742,7 +3806,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN"/>
+              <a:rPr lang="en-IN" b="1"/>
               <a:t>Profitability Trend</a:t>
             </a:r>
           </a:p>
@@ -3761,7 +3825,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1680" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1680" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -3785,7 +3849,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Financial Analysis'!$AB$11</c:f>
+              <c:f>'Financial Analysis'!$AA$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3822,7 +3886,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Financial Analysis'!$AA$12:$AA$16</c:f>
+              <c:f>'Financial Analysis'!$Z$12:$Z$16</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3845,7 +3909,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Financial Analysis'!$AB$12:$AB$16</c:f>
+              <c:f>'Financial Analysis'!$AA$12:$AA$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3879,7 +3943,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Financial Analysis'!$AC$11</c:f>
+              <c:f>'Financial Analysis'!$AB$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3916,7 +3980,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Financial Analysis'!$AA$12:$AA$16</c:f>
+              <c:f>'Financial Analysis'!$Z$12:$Z$16</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -3939,7 +4003,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Financial Analysis'!$AC$12:$AC$16</c:f>
+              <c:f>'Financial Analysis'!$AB$12:$AB$16</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -4169,7 +4233,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1700" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1700" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1"/>
                 </a:solidFill>
@@ -4179,7 +4243,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-IN" sz="1700"/>
+              <a:rPr lang="en-IN" sz="1700" b="1"/>
               <a:t>Cash Flow Trend</a:t>
             </a:r>
           </a:p>
@@ -4198,7 +4262,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1700" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1700" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -4559,6 +4623,564 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1800" b="1"/>
+              <a:t>Market Performance vs Business Performance</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.2006129466525631"/>
+          <c:y val="0"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="&quot;₹&quot;\ #,##0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Financial Analysis'!$J$18:$J$19</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>IPO Issue Price (2021)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Current Share Price (2026)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Financial Analysis'!$M$18:$M$19</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"\ #,##0.00</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0" formatCode="&quot;₹&quot;#,##0.00_);[Red]\(&quot;₹&quot;#,##0.00\)">
+                  <c:v>1125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>314.39999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F212-49CE-96C1-178D82B107AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="400"/>
+        <c:overlap val="-27"/>
+        <c:axId val="740185584"/>
+        <c:axId val="740257328"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="dk1"/>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Financial Analysis'!$J$18:$J$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>IPO Issue Price (2021)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Current Share Price (2026)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Financial Analysis'!$K$18:$K$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-F212-49CE-96C1-178D82B107AC}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="dk1"/>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Financial Analysis'!$J$18:$J$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="2"/>
+                      <c:pt idx="0">
+                        <c:v>IPO Issue Price (2021)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Current Share Price (2026)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Financial Analysis'!$L$18:$L$19</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="2"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-F212-49CE-96C1-178D82B107AC}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="740185584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="740257328"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="740257328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1300"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;₹&quot;#,##0_);[Red]\(&quot;₹&quot;#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="740185584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="300"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4719,6 +5341,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -6731,18 +7393,521 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>-1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>2644</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>169334</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>197557</xdr:rowOff>
     </xdr:to>
@@ -6780,7 +7945,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>564444</xdr:colOff>
+      <xdr:colOff>169334</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>56444</xdr:rowOff>
     </xdr:to>
@@ -6817,8 +7982,8 @@
       <xdr:rowOff>155221</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>84666</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>493889</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>98777</xdr:rowOff>
     </xdr:to>
@@ -6849,16 +8014,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>169332</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>465666</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>112888</xdr:rowOff>
+      <xdr:rowOff>84666</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>14110</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>155222</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>112887</xdr:rowOff>
+      <xdr:rowOff>84665</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6880,6 +8045,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>112889</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>98778</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>56445</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>56444</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38290670-BC94-4A20-9E77-1CBF114641F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7173,277 +8376,277 @@
   <sheetData>
     <row r="1" spans="2:12" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="85"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="94"/>
     </row>
     <row r="3" spans="2:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="88"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="97"/>
     </row>
     <row r="4" spans="2:12" ht="22.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="149" t="s">
+      <c r="B4" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="151"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="100"/>
     </row>
     <row r="5" spans="2:12" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="89"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="154" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="92"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="154"/>
+      <c r="H5" s="154"/>
+      <c r="I5" s="154"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" spans="2:12" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:12" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="197" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="F7" s="9" t="s">
+      <c r="C7" s="198"/>
+      <c r="D7" s="199"/>
+      <c r="F7" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="K7" s="9" t="s">
+      <c r="G7" s="187"/>
+      <c r="H7" s="187"/>
+      <c r="I7" s="147"/>
+      <c r="K7" s="146" t="s">
         <v>136</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="147"/>
     </row>
     <row r="8" spans="2:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="210" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="52"/>
-      <c r="F8" s="25" t="s">
+      <c r="D8" s="211"/>
+      <c r="F8" s="188" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="27"/>
-      <c r="K8" s="254" t="s">
+      <c r="G8" s="189"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="190"/>
+      <c r="K8" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="255"/>
+      <c r="L8" s="149"/>
     </row>
     <row r="9" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="218" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
-      <c r="K9" s="256"/>
-      <c r="L9" s="257"/>
+      <c r="D9" s="219"/>
+      <c r="F9" s="191"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="192"/>
+      <c r="I9" s="193"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="151"/>
     </row>
     <row r="10" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
-      <c r="K10" s="256"/>
-      <c r="L10" s="257"/>
+      <c r="D10" s="215"/>
+      <c r="F10" s="191"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="193"/>
+      <c r="K10" s="150"/>
+      <c r="L10" s="151"/>
     </row>
     <row r="11" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="216" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30"/>
-      <c r="K11" s="256"/>
-      <c r="L11" s="257"/>
+      <c r="D11" s="217"/>
+      <c r="F11" s="191"/>
+      <c r="G11" s="192"/>
+      <c r="H11" s="192"/>
+      <c r="I11" s="193"/>
+      <c r="K11" s="150"/>
+      <c r="L11" s="151"/>
     </row>
     <row r="12" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="214" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="K12" s="256"/>
-      <c r="L12" s="257"/>
+      <c r="D12" s="215"/>
+      <c r="F12" s="191"/>
+      <c r="G12" s="192"/>
+      <c r="H12" s="192"/>
+      <c r="I12" s="193"/>
+      <c r="K12" s="150"/>
+      <c r="L12" s="151"/>
     </row>
     <row r="13" spans="2:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="33"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="259"/>
+      <c r="D13" s="213"/>
+      <c r="F13" s="194"/>
+      <c r="G13" s="195"/>
+      <c r="H13" s="195"/>
+      <c r="I13" s="196"/>
+      <c r="K13" s="152"/>
+      <c r="L13" s="153"/>
     </row>
     <row r="14" spans="2:12" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:12" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="197" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="F15" s="38" t="s">
+      <c r="C15" s="198"/>
+      <c r="D15" s="199"/>
+      <c r="F15" s="165" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="K15" s="38" t="s">
+      <c r="G15" s="183"/>
+      <c r="H15" s="183"/>
+      <c r="I15" s="166"/>
+      <c r="K15" s="165" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="40"/>
+      <c r="L15" s="166"/>
     </row>
     <row r="16" spans="2:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="43"/>
-      <c r="F16" s="53" t="s">
+      <c r="C16" s="201"/>
+      <c r="D16" s="202"/>
+      <c r="F16" s="186" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54" t="s">
+      <c r="G16" s="181"/>
+      <c r="H16" s="181" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="55"/>
-      <c r="K16" s="56" t="s">
+      <c r="I16" s="182"/>
+      <c r="K16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="L16" s="57" t="s">
+      <c r="L16" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="46"/>
-      <c r="F17" s="34" t="s">
+      <c r="B17" s="203"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="205"/>
+      <c r="F17" s="185" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58" t="s">
+      <c r="G17" s="179"/>
+      <c r="H17" s="179" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="59"/>
-      <c r="K17" s="63" t="s">
+      <c r="I17" s="180"/>
+      <c r="K17" s="167" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="63" t="s">
+      <c r="L17" s="167" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="44"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="46"/>
-      <c r="F18" s="19" t="s">
+      <c r="B18" s="203"/>
+      <c r="C18" s="204"/>
+      <c r="D18" s="205"/>
+      <c r="F18" s="184" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20" t="s">
+      <c r="G18" s="177"/>
+      <c r="H18" s="177" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="21"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
+      <c r="I18" s="178"/>
+      <c r="K18" s="168"/>
+      <c r="L18" s="168"/>
     </row>
     <row r="19" spans="2:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="44"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="46"/>
-      <c r="F19" s="19" t="s">
+      <c r="B19" s="203"/>
+      <c r="C19" s="204"/>
+      <c r="D19" s="205"/>
+      <c r="F19" s="184" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20" t="s">
+      <c r="G19" s="177"/>
+      <c r="H19" s="177" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="21"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
+      <c r="I19" s="178"/>
+      <c r="K19" s="168"/>
+      <c r="L19" s="168"/>
     </row>
     <row r="20" spans="2:12" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="47"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="F20" s="60" t="s">
+      <c r="B20" s="206"/>
+      <c r="C20" s="207"/>
+      <c r="D20" s="208"/>
+      <c r="F20" s="209" t="s">
         <v>24</v>
       </c>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61" t="s">
+      <c r="G20" s="175"/>
+      <c r="H20" s="175" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="62"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
+      <c r="I20" s="176"/>
+      <c r="K20" s="169"/>
+      <c r="L20" s="169"/>
     </row>
     <row r="21" spans="2:12" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
@@ -7451,77 +8654,100 @@
       <c r="D21" s="5"/>
     </row>
     <row r="22" spans="2:12" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="70"/>
-      <c r="D22" s="66" t="s">
+      <c r="C22" s="171"/>
+      <c r="D22" s="172" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="68"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="174"/>
     </row>
     <row r="23" spans="2:12" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="2:12" s="12" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="71" t="s">
+    <row r="24" spans="2:12" s="6" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="155" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="93" t="s">
+      <c r="C24" s="156"/>
+      <c r="D24" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="94"/>
-      <c r="F24" s="75" t="s">
+      <c r="E24" s="162"/>
+      <c r="F24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="76" t="s">
+      <c r="G24" s="164" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76" t="s">
+      <c r="H24" s="164"/>
+      <c r="I24" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="J24" s="76"/>
-      <c r="K24" s="77" t="s">
+      <c r="J24" s="164"/>
+      <c r="K24" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="L24" s="78" t="s">
+      <c r="L24" s="16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="12" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="72"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="95" t="s">
+    <row r="25" spans="2:12" s="6" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="157"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="79" t="s">
+      <c r="E25" s="160"/>
+      <c r="F25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="80" t="s">
+      <c r="G25" s="163" t="s">
         <v>39</v>
       </c>
-      <c r="H25" s="80"/>
-      <c r="I25" s="80" t="s">
+      <c r="H25" s="163"/>
+      <c r="I25" s="163" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="80"/>
-      <c r="K25" s="81" t="s">
+      <c r="J25" s="163"/>
+      <c r="K25" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="L25" s="82" t="s">
+      <c r="L25" s="19" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B16:D20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="F8:I13"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L13"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F16:G16"/>
     <mergeCell ref="B2:L3"/>
     <mergeCell ref="B4:L4"/>
     <mergeCell ref="D5:I5"/>
@@ -7538,29 +8764,6 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:L22"/>
     <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="F8:I13"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L13"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7568,7 +8771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F4DE87E-E191-45BB-AE18-63E32D2B1847}">
-  <dimension ref="B1:Q48"/>
+  <dimension ref="B1:K48"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.23046875" style="3" customWidth="1"/>
@@ -7582,840 +8785,834 @@
   <sheetData>
     <row r="1" spans="2:11" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:11" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="94"/>
     </row>
     <row r="3" spans="2:11" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="88"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="97"/>
     </row>
     <row r="4" spans="2:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="149" t="s">
+      <c r="B4" s="98" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="151"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="100"/>
     </row>
     <row r="5" spans="2:11" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" spans="2:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="227" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="147"/>
-      <c r="D6" s="147"/>
-      <c r="E6" s="147"/>
-      <c r="F6" s="147"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="147"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="101"/>
+      <c r="C6" s="228"/>
+      <c r="D6" s="228"/>
+      <c r="E6" s="228"/>
+      <c r="F6" s="228"/>
+      <c r="G6" s="228"/>
+      <c r="H6" s="228"/>
+      <c r="I6" s="228"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="23"/>
     </row>
     <row r="7" spans="2:11" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="2:11" s="118" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B8" s="115" t="s">
+    <row r="8" spans="2:11" s="36" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B8" s="230" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="117"/>
-      <c r="I8" s="152" t="s">
+      <c r="C8" s="231"/>
+      <c r="D8" s="231"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="231"/>
+      <c r="G8" s="232"/>
+      <c r="I8" s="220" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="153"/>
-    </row>
-    <row r="9" spans="2:11" s="113" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="105" t="s">
+      <c r="J8" s="221"/>
+    </row>
+    <row r="9" spans="2:11" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="106" t="s">
+      <c r="C9" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="106" t="s">
+      <c r="E9" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="108" t="s">
+      <c r="G9" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="154"/>
-      <c r="J9" s="155"/>
+      <c r="I9" s="222"/>
+      <c r="J9" s="223"/>
     </row>
     <row r="10" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="135">
+      <c r="C10" s="47">
         <v>3774</v>
       </c>
-      <c r="D10" s="135">
+      <c r="D10" s="47">
         <v>5144</v>
       </c>
-      <c r="E10" s="135">
+      <c r="E10" s="47">
         <v>6386</v>
       </c>
-      <c r="F10" s="135">
+      <c r="F10" s="47">
         <v>7950</v>
       </c>
-      <c r="G10" s="136">
+      <c r="G10" s="48">
         <v>10022</v>
       </c>
-      <c r="I10" s="154"/>
-      <c r="J10" s="155"/>
+      <c r="I10" s="222"/>
+      <c r="J10" s="223"/>
     </row>
     <row r="11" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="120" t="s">
+      <c r="B11" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="137">
+      <c r="C11" s="49">
         <v>27</v>
       </c>
-      <c r="D11" s="137">
+      <c r="D11" s="49">
         <v>30</v>
       </c>
-      <c r="E11" s="137">
+      <c r="E11" s="49">
         <v>30</v>
       </c>
-      <c r="F11" s="137">
+      <c r="F11" s="49">
         <v>27</v>
       </c>
-      <c r="G11" s="138">
+      <c r="G11" s="50">
         <v>15</v>
       </c>
-      <c r="I11" s="154"/>
-      <c r="J11" s="155"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="223"/>
     </row>
     <row r="12" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="121" t="s">
+      <c r="B12" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="139">
+      <c r="C12" s="51">
         <v>3801</v>
       </c>
-      <c r="D12" s="139">
+      <c r="D12" s="51">
         <v>5174</v>
       </c>
-      <c r="E12" s="139">
+      <c r="E12" s="51">
         <v>6416</v>
       </c>
-      <c r="F12" s="139">
+      <c r="F12" s="51">
         <v>7977</v>
       </c>
-      <c r="G12" s="140">
+      <c r="G12" s="52">
         <v>10037</v>
       </c>
-      <c r="I12" s="154"/>
-      <c r="J12" s="155"/>
+      <c r="I12" s="222"/>
+      <c r="J12" s="223"/>
     </row>
     <row r="13" spans="2:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="137">
+      <c r="C13" s="49">
         <v>190.23</v>
       </c>
-      <c r="D13" s="137">
+      <c r="D13" s="49">
         <v>286.26</v>
       </c>
-      <c r="E13" s="137">
+      <c r="E13" s="49">
         <v>376.09</v>
       </c>
-      <c r="F13" s="137">
+      <c r="F13" s="49">
         <v>501.17</v>
       </c>
-      <c r="G13" s="138" t="s">
+      <c r="G13" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="I13" s="156"/>
-      <c r="J13" s="157"/>
+      <c r="I13" s="224"/>
+      <c r="J13" s="225"/>
     </row>
     <row r="14" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="137">
+      <c r="C14" s="49">
         <v>164</v>
       </c>
-      <c r="D14" s="137">
+      <c r="D14" s="49">
         <v>257</v>
       </c>
-      <c r="E14" s="137">
+      <c r="E14" s="49">
         <v>347</v>
       </c>
-      <c r="F14" s="137">
+      <c r="F14" s="49">
         <v>475</v>
       </c>
-      <c r="G14" s="138">
+      <c r="G14" s="50">
         <v>752</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="120" t="s">
+      <c r="B15" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="137">
+      <c r="C15" s="49">
         <v>47</v>
       </c>
-      <c r="D15" s="137">
+      <c r="D15" s="49">
         <v>76</v>
       </c>
-      <c r="E15" s="137">
+      <c r="E15" s="49">
         <v>84</v>
       </c>
-      <c r="F15" s="137">
+      <c r="F15" s="49">
         <v>108</v>
       </c>
-      <c r="G15" s="138">
+      <c r="G15" s="50">
         <v>117</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="120" t="s">
+      <c r="B16" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="137">
+      <c r="C16" s="49">
         <v>96</v>
       </c>
-      <c r="D16" s="137">
+      <c r="D16" s="49">
         <v>173</v>
       </c>
-      <c r="E16" s="137">
+      <c r="E16" s="49">
         <v>224</v>
       </c>
-      <c r="F16" s="137">
+      <c r="F16" s="49">
         <v>266</v>
       </c>
-      <c r="G16" s="138">
+      <c r="G16" s="50">
         <v>320</v>
       </c>
     </row>
-    <row r="17" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="120" t="s">
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="137">
+      <c r="C17" s="49">
         <v>47</v>
       </c>
-      <c r="D17" s="137">
+      <c r="D17" s="49">
         <v>38</v>
       </c>
-      <c r="E17" s="137">
+      <c r="E17" s="49">
         <v>69</v>
       </c>
-      <c r="F17" s="137">
+      <c r="F17" s="49">
         <v>127</v>
       </c>
-      <c r="G17" s="138">
+      <c r="G17" s="50">
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="120" t="s">
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="137">
+      <c r="C18" s="49">
         <v>41</v>
       </c>
-      <c r="D18" s="137">
+      <c r="D18" s="49">
         <v>21</v>
       </c>
-      <c r="E18" s="137">
+      <c r="E18" s="49">
         <v>40</v>
       </c>
-      <c r="F18" s="137">
+      <c r="F18" s="49">
         <v>72</v>
       </c>
-      <c r="G18" s="138">
+      <c r="G18" s="50">
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="2:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="122" t="s">
+    <row r="19" spans="2:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="141">
+      <c r="C19" s="53">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D19" s="141">
+      <c r="D19" s="53">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="E19" s="141">
+      <c r="E19" s="53">
         <v>0.11</v>
       </c>
-      <c r="F19" s="141">
+      <c r="F19" s="53">
         <v>0.23</v>
       </c>
-      <c r="G19" s="142">
+      <c r="G19" s="54">
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="283" t="s">
+    <row r="20" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="226" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="283"/>
-      <c r="D20" s="283"/>
-      <c r="E20" s="283"/>
-      <c r="F20" s="283"/>
-      <c r="G20" s="283"/>
-    </row>
-    <row r="21" spans="2:17" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:17" s="118" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B22" s="115" t="s">
+      <c r="C20" s="226"/>
+      <c r="D20" s="226"/>
+      <c r="E20" s="226"/>
+      <c r="F20" s="226"/>
+      <c r="G20" s="226"/>
+    </row>
+    <row r="21" spans="2:7" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:7" s="36" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="230" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="117"/>
-    </row>
-    <row r="23" spans="2:17" s="113" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="112" t="s">
+      <c r="C22" s="231"/>
+      <c r="D22" s="231"/>
+      <c r="E22" s="231"/>
+      <c r="F22" s="231"/>
+      <c r="G22" s="232"/>
+    </row>
+    <row r="23" spans="2:7" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="109" t="s">
+      <c r="C23" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="109" t="s">
+      <c r="D23" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="109" t="s">
+      <c r="E23" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F23" s="110" t="s">
+      <c r="F23" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="111" t="s">
+      <c r="G23" s="32" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="119" t="s">
+    <row r="24" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="143">
+      <c r="C24" s="55">
         <v>267</v>
       </c>
-      <c r="D24" s="143">
+      <c r="D24" s="55">
         <v>149</v>
       </c>
-      <c r="E24" s="143">
+      <c r="E24" s="55">
         <v>240</v>
       </c>
-      <c r="F24" s="143">
+      <c r="F24" s="55">
         <v>217</v>
       </c>
-      <c r="G24" s="144" t="s">
+      <c r="G24" s="56" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="2:17" s="97" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="120" t="s">
+    <row r="25" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="137">
+      <c r="C25" s="49">
         <v>95</v>
       </c>
-      <c r="D25" s="137">
+      <c r="D25" s="49">
         <v>164</v>
       </c>
-      <c r="E25" s="137">
+      <c r="E25" s="49">
         <v>242</v>
       </c>
-      <c r="F25" s="137">
+      <c r="F25" s="49">
         <v>247</v>
       </c>
-      <c r="G25" s="138" t="s">
+      <c r="G25" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="120" t="s">
+    </row>
+    <row r="26" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="137">
+      <c r="C26" s="49">
         <v>876</v>
       </c>
-      <c r="D26" s="137">
+      <c r="D26" s="49">
         <v>1005</v>
       </c>
-      <c r="E26" s="137">
+      <c r="E26" s="49">
         <v>1192</v>
       </c>
-      <c r="F26" s="137">
+      <c r="F26" s="49">
         <v>1418</v>
       </c>
-      <c r="G26" s="138" t="s">
+      <c r="G26" s="50" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="120" t="s">
+    <row r="27" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="137">
+      <c r="C27" s="49">
         <v>690</v>
       </c>
-      <c r="D27" s="137">
+      <c r="D27" s="49">
         <v>588</v>
       </c>
-      <c r="E27" s="137">
+      <c r="E27" s="49">
         <v>620</v>
       </c>
-      <c r="F27" s="137">
+      <c r="F27" s="49">
         <v>796</v>
       </c>
-      <c r="G27" s="138" t="s">
+      <c r="G27" s="50" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="121" t="s">
+    <row r="28" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="139">
+      <c r="C28" s="51">
         <v>1927</v>
       </c>
-      <c r="D28" s="139">
+      <c r="D28" s="51">
         <v>1906</v>
       </c>
-      <c r="E28" s="139">
+      <c r="E28" s="51">
         <v>2293</v>
       </c>
-      <c r="F28" s="139">
+      <c r="F28" s="51">
         <v>2677</v>
       </c>
-      <c r="G28" s="138" t="s">
+      <c r="G28" s="50" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="120" t="s">
+    <row r="29" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="137">
+      <c r="C29" s="49">
         <v>382</v>
       </c>
-      <c r="D29" s="137">
+      <c r="D29" s="49">
         <v>545</v>
       </c>
-      <c r="E29" s="137">
+      <c r="E29" s="49">
         <v>503</v>
       </c>
-      <c r="F29" s="137">
+      <c r="F29" s="49">
         <v>605</v>
       </c>
-      <c r="G29" s="138" t="s">
+      <c r="G29" s="50" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="120" t="s">
+    <row r="30" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="137">
+      <c r="C30" s="49">
         <v>719</v>
       </c>
-      <c r="D30" s="137">
+      <c r="D30" s="49">
         <v>1044</v>
       </c>
-      <c r="E30" s="137">
+      <c r="E30" s="49">
         <v>1108</v>
       </c>
-      <c r="F30" s="137">
+      <c r="F30" s="49">
         <v>1302</v>
       </c>
-      <c r="G30" s="138" t="s">
+      <c r="G30" s="50" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="121" t="s">
+    <row r="31" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="139">
+      <c r="C31" s="51">
         <v>2646</v>
       </c>
-      <c r="D31" s="139">
+      <c r="D31" s="51">
         <v>2950</v>
       </c>
-      <c r="E31" s="139">
+      <c r="E31" s="51">
         <v>3401</v>
       </c>
-      <c r="F31" s="139">
+      <c r="F31" s="51">
         <v>3980</v>
       </c>
-      <c r="G31" s="140">
+      <c r="G31" s="52">
         <v>4611</v>
       </c>
     </row>
-    <row r="32" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="120" t="s">
+    <row r="32" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="137">
+      <c r="C32" s="49">
         <v>362</v>
       </c>
-      <c r="D32" s="137">
+      <c r="D32" s="49">
         <v>265</v>
       </c>
-      <c r="E32" s="137">
+      <c r="E32" s="49">
         <v>387</v>
       </c>
-      <c r="F32" s="137">
+      <c r="F32" s="49">
         <v>635</v>
       </c>
-      <c r="G32" s="138" t="s">
+      <c r="G32" s="50" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="120" t="s">
+      <c r="B33" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="137">
+      <c r="C33" s="49">
         <v>593</v>
       </c>
-      <c r="D33" s="137">
+      <c r="D33" s="49">
         <v>798</v>
       </c>
-      <c r="E33" s="137">
+      <c r="E33" s="49">
         <v>969</v>
       </c>
-      <c r="F33" s="137">
+      <c r="F33" s="49">
         <v>1321</v>
       </c>
-      <c r="G33" s="138">
+      <c r="G33" s="50">
         <v>1238</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="120" t="s">
+      <c r="B34" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="137">
+      <c r="C34" s="49">
         <v>714</v>
       </c>
-      <c r="D34" s="137">
+      <c r="D34" s="49">
         <v>773</v>
       </c>
-      <c r="E34" s="137">
+      <c r="E34" s="49">
         <v>1169</v>
       </c>
-      <c r="F34" s="137">
+      <c r="F34" s="49">
         <v>1358</v>
       </c>
-      <c r="G34" s="138">
+      <c r="G34" s="50">
         <v>1936</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="121" t="s">
+      <c r="B35" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="139">
+      <c r="C35" s="51">
         <v>2646</v>
       </c>
-      <c r="D35" s="139">
+      <c r="D35" s="51">
         <v>2950</v>
       </c>
-      <c r="E35" s="139">
+      <c r="E35" s="51">
         <v>3401</v>
       </c>
-      <c r="F35" s="139">
+      <c r="F35" s="51">
         <v>3980</v>
       </c>
-      <c r="G35" s="140">
+      <c r="G35" s="52">
         <v>4611</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="137">
+      <c r="C36" s="49">
         <v>47</v>
       </c>
-      <c r="D36" s="137">
+      <c r="D36" s="49">
         <v>285</v>
       </c>
-      <c r="E36" s="137">
+      <c r="E36" s="49">
         <v>286</v>
       </c>
-      <c r="F36" s="137">
+      <c r="F36" s="49">
         <v>286</v>
       </c>
-      <c r="G36" s="138">
+      <c r="G36" s="50">
         <v>286</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="213" t="s">
+      <c r="B37" s="77" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="214">
+      <c r="C37" s="78">
         <v>1292</v>
       </c>
-      <c r="D37" s="214">
+      <c r="D37" s="78">
         <v>1093</v>
       </c>
-      <c r="E37" s="214">
+      <c r="E37" s="78">
         <v>977</v>
       </c>
-      <c r="F37" s="214">
+      <c r="F37" s="78">
         <v>1015</v>
       </c>
-      <c r="G37" s="215">
+      <c r="G37" s="79">
         <v>1152</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="216" t="s">
+      <c r="B38" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="217">
+      <c r="C38" s="81">
         <f>C36+C37</f>
         <v>1339</v>
       </c>
-      <c r="D38" s="217">
+      <c r="D38" s="81">
         <f t="shared" ref="D38:G38" si="0">D36+D37</f>
         <v>1378</v>
       </c>
-      <c r="E38" s="217">
+      <c r="E38" s="81">
         <f t="shared" si="0"/>
         <v>1263</v>
       </c>
-      <c r="F38" s="217">
+      <c r="F38" s="81">
         <f t="shared" si="0"/>
         <v>1301</v>
       </c>
-      <c r="G38" s="145">
+      <c r="G38" s="57">
         <f t="shared" si="0"/>
         <v>1438</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="10.050000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="2:7" s="118" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B40" s="115" t="s">
+    <row r="40" spans="2:7" s="36" customFormat="1" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B40" s="230" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="116"/>
-      <c r="D40" s="116"/>
-      <c r="E40" s="116"/>
-      <c r="F40" s="116"/>
-      <c r="G40" s="117"/>
-    </row>
-    <row r="41" spans="2:7" s="113" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="112" t="s">
+      <c r="C40" s="231"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="232"/>
+    </row>
+    <row r="41" spans="2:7" s="34" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C41" s="109" t="s">
+      <c r="C41" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="109" t="s">
+      <c r="D41" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="E41" s="109" t="s">
+      <c r="E41" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="F41" s="110" t="s">
+      <c r="F41" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="111" t="s">
+      <c r="G41" s="32" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="123" t="s">
+      <c r="B42" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="158">
+      <c r="C42" s="58">
         <v>67</v>
       </c>
-      <c r="D42" s="158">
+      <c r="D42" s="58">
         <v>37</v>
       </c>
-      <c r="E42" s="158">
+      <c r="E42" s="58">
         <v>41</v>
       </c>
-      <c r="F42" s="158">
+      <c r="F42" s="58">
         <v>76</v>
       </c>
-      <c r="G42" s="159">
+      <c r="G42" s="59">
         <v>125</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="120" t="s">
+      <c r="B43" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C43" s="191">
+      <c r="C43" s="74">
         <v>-354</v>
       </c>
-      <c r="D43" s="191">
+      <c r="D43" s="74">
         <v>-140</v>
       </c>
-      <c r="E43" s="191">
+      <c r="E43" s="74">
         <v>0</v>
       </c>
-      <c r="F43" s="191">
+      <c r="F43" s="74">
         <v>467</v>
       </c>
-      <c r="G43" s="190">
+      <c r="G43" s="73">
         <v>644</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="120" t="s">
+      <c r="B44" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="191">
+      <c r="C44" s="74">
         <v>-603</v>
       </c>
-      <c r="D44" s="191">
+      <c r="D44" s="74">
         <v>140</v>
       </c>
-      <c r="E44" s="191">
+      <c r="E44" s="74">
         <v>-10</v>
       </c>
-      <c r="F44" s="191">
+      <c r="F44" s="74">
         <v>-205</v>
       </c>
-      <c r="G44" s="190">
+      <c r="G44" s="73">
         <v>-159</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="120" t="s">
+      <c r="B45" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="C45" s="191">
+      <c r="C45" s="74">
         <v>927</v>
       </c>
-      <c r="D45" s="191">
+      <c r="D45" s="74">
         <v>5</v>
       </c>
-      <c r="E45" s="191">
+      <c r="E45" s="74">
         <v>44</v>
       </c>
-      <c r="F45" s="191">
+      <c r="F45" s="74">
         <v>-212</v>
       </c>
-      <c r="G45" s="190">
+      <c r="G45" s="73">
         <v>-433</v>
       </c>
     </row>
     <row r="46" spans="2:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="120" t="s">
+      <c r="B46" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C46" s="191">
+      <c r="C46" s="74">
         <v>-30</v>
       </c>
-      <c r="D46" s="191">
+      <c r="D46" s="74">
         <v>4</v>
       </c>
-      <c r="E46" s="191">
+      <c r="E46" s="74">
         <v>34</v>
       </c>
-      <c r="F46" s="191">
+      <c r="F46" s="74">
         <v>49</v>
       </c>
-      <c r="G46" s="190">
+      <c r="G46" s="73">
         <v>52</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="125" t="s">
+      <c r="B47" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="160">
+      <c r="C47" s="60">
         <v>37</v>
       </c>
-      <c r="D47" s="160">
+      <c r="D47" s="60">
         <v>41</v>
       </c>
-      <c r="E47" s="160">
+      <c r="E47" s="60">
         <v>76</v>
       </c>
-      <c r="F47" s="160">
+      <c r="F47" s="60">
         <v>125</v>
       </c>
-      <c r="G47" s="161" t="s">
+      <c r="G47" s="61" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="162">
+      <c r="C48" s="62">
         <v>-448</v>
       </c>
-      <c r="D48" s="162">
+      <c r="D48" s="62">
         <v>-348</v>
       </c>
-      <c r="E48" s="162">
+      <c r="E48" s="62">
         <v>-110</v>
       </c>
-      <c r="F48" s="162">
+      <c r="F48" s="62">
         <v>339</v>
       </c>
-      <c r="G48" s="163">
+      <c r="G48" s="63">
         <v>493</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B40:G40"/>
     <mergeCell ref="I8:J13"/>
     <mergeCell ref="B2:J3"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B20:G20"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B40:G40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8426,60 +9623,63 @@
   <dimension ref="B1:AF23"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="186" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="186"/>
-    <col min="4" max="5" width="11" style="186" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.23046875" style="186"/>
-    <col min="9" max="9" width="2.69140625" style="186" customWidth="1"/>
-    <col min="10" max="16384" width="9.23046875" style="186"/>
+    <col min="1" max="1" width="2.15234375" style="69" customWidth="1"/>
+    <col min="2" max="3" width="9.23046875" style="69"/>
+    <col min="4" max="5" width="11" style="69" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.23046875" style="69"/>
+    <col min="9" max="9" width="1.765625" style="69" customWidth="1"/>
+    <col min="10" max="12" width="9.23046875" style="69"/>
+    <col min="13" max="13" width="11.921875" style="69" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2" style="69" customWidth="1"/>
+    <col min="15" max="16384" width="9.23046875" style="69"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:32" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:32" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="85"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="94"/>
     </row>
     <row r="3" spans="2:32" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="88"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="97"/>
     </row>
     <row r="4" spans="2:32" ht="19.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="149" t="s">
+      <c r="B4" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="150"/>
-      <c r="M4" s="151"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="100"/>
     </row>
     <row r="5" spans="2:32" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AA5" s="1" t="s">
@@ -8491,602 +9691,622 @@
       <c r="AD5" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AE5" s="103" t="s">
+      <c r="AE5" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="AF5" s="103" t="s">
+      <c r="AF5" s="25" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="2:32" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="256" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="100"/>
-      <c r="J6" s="196" t="s">
+      <c r="C6" s="257"/>
+      <c r="D6" s="257"/>
+      <c r="E6" s="257"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="258"/>
+      <c r="J6" s="237" t="s">
         <v>119</v>
       </c>
-      <c r="K6" s="197"/>
-      <c r="L6" s="197"/>
-      <c r="M6" s="198"/>
+      <c r="K6" s="238"/>
+      <c r="L6" s="238"/>
+      <c r="M6" s="239"/>
       <c r="AA6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB6" s="232">
+      <c r="AB6" s="89">
         <v>0.36299999999999999</v>
       </c>
       <c r="AD6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AE6" s="102">
+      <c r="AE6" s="24">
         <v>-354</v>
       </c>
-      <c r="AF6" s="102">
+      <c r="AF6" s="24">
         <v>-448</v>
       </c>
     </row>
-    <row r="7" spans="2:32" s="187" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="164" t="s">
+    <row r="7" spans="2:32" s="70" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="165"/>
-      <c r="D7" s="166" t="s">
+      <c r="C7" s="144"/>
+      <c r="D7" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="166" t="s">
+      <c r="E7" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="166" t="s">
+      <c r="F7" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="166" t="s">
+      <c r="G7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="167" t="s">
+      <c r="H7" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="J7" s="192" t="s">
+      <c r="J7" s="233" t="s">
         <v>111</v>
       </c>
-      <c r="K7" s="193"/>
-      <c r="L7" s="194" t="s">
+      <c r="K7" s="234"/>
+      <c r="L7" s="235" t="s">
         <v>112</v>
       </c>
-      <c r="M7" s="195"/>
+      <c r="M7" s="236"/>
       <c r="AA7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB7" s="232">
+      <c r="AB7" s="89">
         <v>0.2414</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AE7" s="102">
+      <c r="AE7" s="24">
         <v>-140</v>
       </c>
-      <c r="AF7" s="102">
+      <c r="AF7" s="24">
         <v>-348</v>
       </c>
     </row>
-    <row r="8" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="180" t="s">
+    <row r="8" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="251" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="181"/>
-      <c r="D8" s="175" t="s">
+      <c r="C8" s="252"/>
+      <c r="D8" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="E8" s="175">
+      <c r="E8" s="66">
         <f>('Financial Data'!D10-'Financial Data'!C10)/'Financial Data'!C10</f>
         <v>0.36301006889242182</v>
       </c>
-      <c r="F8" s="175">
+      <c r="F8" s="66">
         <f>('Financial Data'!E10-'Financial Data'!D10)/'Financial Data'!D10</f>
         <v>0.24144634525660963</v>
       </c>
-      <c r="G8" s="175">
+      <c r="G8" s="66">
         <f>('Financial Data'!F10-'Financial Data'!E10)/'Financial Data'!E10</f>
         <v>0.24491074224866896</v>
       </c>
-      <c r="H8" s="199">
+      <c r="H8" s="75">
         <f>('Financial Data'!G10-'Financial Data'!F10)/'Financial Data'!F10</f>
         <v>0.26062893081761007</v>
       </c>
-      <c r="J8" s="180" t="s">
+      <c r="J8" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="K8" s="181"/>
-      <c r="L8" s="169" t="str">
+      <c r="K8" s="252"/>
+      <c r="L8" s="245" t="str">
         <f>IF(AVERAGE(C8:G8)&gt;0.2,"Strong"," Moderate")</f>
         <v>Strong</v>
       </c>
-      <c r="M8" s="172"/>
+      <c r="M8" s="246"/>
+      <c r="O8" s="101" t="s">
+        <v>120</v>
+      </c>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="103"/>
       <c r="AA8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AB8" s="232">
+      <c r="AB8" s="89">
         <v>0.24490000000000001</v>
       </c>
       <c r="AD8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AE8" s="102">
+      <c r="AE8" s="24">
         <v>0</v>
       </c>
-      <c r="AF8" s="102">
+      <c r="AF8" s="24">
         <v>-110</v>
       </c>
     </row>
-    <row r="9" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="124" t="s">
+    <row r="9" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="249" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="182"/>
-      <c r="D9" s="176">
+      <c r="C9" s="250"/>
+      <c r="D9" s="240">
         <f>('Financial Data'!G10/'Financial Data'!C10)^(1/5)-1</f>
         <v>0.21571143169251283</v>
       </c>
-      <c r="E9" s="177"/>
-      <c r="F9" s="177"/>
-      <c r="G9" s="177"/>
-      <c r="H9" s="178"/>
-      <c r="J9" s="124" t="s">
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="242"/>
+      <c r="J9" s="249" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="182"/>
-      <c r="L9" s="170" t="str">
+      <c r="K9" s="250"/>
+      <c r="L9" s="243" t="str">
         <f>IF(G15&gt;5%," Improving"," Stable")</f>
         <v xml:space="preserve"> Stable</v>
       </c>
-      <c r="M9" s="173"/>
+      <c r="M9" s="244"/>
+      <c r="O9" s="280" t="s">
+        <v>121</v>
+      </c>
+      <c r="P9" s="281"/>
+      <c r="Q9" s="286"/>
       <c r="AA9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AB9" s="232">
+      <c r="AB9" s="89">
         <v>0.2606</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AE9" s="102">
+      <c r="AE9" s="24">
         <v>467</v>
       </c>
-      <c r="AF9" s="102">
+      <c r="AF9" s="24">
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="183" t="s">
+    <row r="10" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="247" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="184"/>
-      <c r="D10" s="179" t="s">
+      <c r="C10" s="248"/>
+      <c r="D10" s="67" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="179">
+      <c r="E10" s="67">
         <f>('Financial Data'!D31-'Financial Data'!C31)/'Financial Data'!D31</f>
         <v>0.10305084745762712</v>
       </c>
-      <c r="F10" s="179">
+      <c r="F10" s="67">
         <f>('Financial Data'!E31-'Financial Data'!D31)/'Financial Data'!E31</f>
         <v>0.13260805645398413</v>
       </c>
-      <c r="G10" s="179">
+      <c r="G10" s="67">
         <f>('Financial Data'!F31-'Financial Data'!E31)/'Financial Data'!F31</f>
         <v>0.14547738693467338</v>
       </c>
-      <c r="H10" s="200">
+      <c r="H10" s="76">
         <f>('Financial Data'!G31-'Financial Data'!F31)/'Financial Data'!G31</f>
         <v>0.13684667100412057</v>
       </c>
-      <c r="J10" s="124" t="s">
+      <c r="J10" s="249" t="s">
         <v>113</v>
       </c>
-      <c r="K10" s="182"/>
-      <c r="L10" s="170" t="str">
+      <c r="K10" s="250"/>
+      <c r="L10" s="243" t="str">
         <f>IF(G22&gt;0,"Positive","Weak")</f>
         <v>Positive</v>
       </c>
-      <c r="M10" s="173"/>
+      <c r="M10" s="244"/>
+      <c r="O10" s="282"/>
+      <c r="P10" s="283"/>
+      <c r="Q10" s="287"/>
       <c r="AD10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AE10" s="102">
+      <c r="AE10" s="24">
         <v>644</v>
       </c>
-      <c r="AF10" s="102">
+      <c r="AF10" s="24">
         <v>493</v>
       </c>
     </row>
     <row r="11" spans="2:32" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J11" s="124" t="s">
+      <c r="J11" s="249" t="s">
         <v>114</v>
       </c>
-      <c r="K11" s="182"/>
-      <c r="L11" s="170" t="str">
+      <c r="K11" s="250"/>
+      <c r="L11" s="243" t="str">
         <f>IF(G24&lt;1,"Healthy","Moderate")</f>
         <v>Healthy</v>
       </c>
-      <c r="M11" s="173"/>
-      <c r="AA11" s="1" t="s">
+      <c r="M11" s="244"/>
+      <c r="O11" s="282"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="287"/>
+      <c r="Z11" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AB11" s="103" t="s">
+      <c r="AA11" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="AC11" s="103" t="s">
+      <c r="AB11" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:32" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="256" t="s">
         <v>117</v>
       </c>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="100"/>
-      <c r="J12" s="183" t="s">
+      <c r="C12" s="257"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="257"/>
+      <c r="F12" s="257"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="258"/>
+      <c r="J12" s="247" t="s">
         <v>115</v>
       </c>
-      <c r="K12" s="184"/>
-      <c r="L12" s="171" t="str">
+      <c r="K12" s="248"/>
+      <c r="L12" s="253" t="str">
         <f>IF(COUNTIF(L8:M11,"*")&gt;=3,"Positive","Mixed")</f>
         <v>Positive</v>
       </c>
-      <c r="M12" s="174"/>
-      <c r="AA12" s="2" t="s">
+      <c r="M12" s="254"/>
+      <c r="O12" s="282"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="287"/>
+      <c r="Z12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="AB12" s="233">
+      <c r="AA12" s="90">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="AC12" s="233">
+      <c r="AB12" s="90">
         <v>1.09E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:32" s="187" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="164" t="s">
+    <row r="13" spans="2:32" s="70" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166" t="s">
+      <c r="C13" s="144"/>
+      <c r="D13" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="166" t="s">
+      <c r="E13" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="166" t="s">
+      <c r="F13" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="166" t="s">
+      <c r="G13" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="167" t="s">
+      <c r="H13" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="AA13" s="2" t="s">
+      <c r="O13" s="282"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="287"/>
+      <c r="Z13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="AB13" s="233">
+      <c r="AA13" s="90">
         <v>0.05</v>
       </c>
-      <c r="AC13" s="233">
+      <c r="AB13" s="90">
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="14" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="180" t="s">
+    <row r="14" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="251" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="181"/>
-      <c r="D14" s="175">
+      <c r="C14" s="252"/>
+      <c r="D14" s="66">
         <f>'Financial Data'!C14/'Financial Data'!C10</f>
         <v>4.3455219925808163E-2</v>
       </c>
-      <c r="E14" s="175">
+      <c r="E14" s="66">
         <f>'Financial Data'!D14/'Financial Data'!D10</f>
         <v>4.9961119751166405E-2</v>
       </c>
-      <c r="F14" s="175">
+      <c r="F14" s="66">
         <f>'Financial Data'!E14/'Financial Data'!E10</f>
         <v>5.4337613529595992E-2</v>
       </c>
-      <c r="G14" s="175">
+      <c r="G14" s="66">
         <f>'Financial Data'!F14/'Financial Data'!F10</f>
         <v>5.9748427672955975E-2</v>
       </c>
-      <c r="H14" s="175">
+      <c r="H14" s="66">
         <f>'Financial Data'!G14/'Financial Data'!G10</f>
         <v>7.5034923169028142E-2</v>
       </c>
-      <c r="J14" s="201" t="s">
-        <v>120</v>
-      </c>
-      <c r="K14" s="202"/>
-      <c r="L14" s="202"/>
-      <c r="M14" s="203"/>
-      <c r="AA14" s="2" t="s">
+      <c r="O14" s="282"/>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="287"/>
+      <c r="Z14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="AB14" s="233">
+      <c r="AA14" s="90">
         <v>5.4300000000000001E-2</v>
       </c>
-      <c r="AC14" s="233">
+      <c r="AB14" s="90">
         <v>6.3E-3</v>
       </c>
     </row>
-    <row r="15" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="124" t="s">
+    <row r="15" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="249" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="182"/>
-      <c r="D15" s="185">
+      <c r="C15" s="250"/>
+      <c r="D15" s="68">
         <f>'Financial Data'!C18/'Financial Data'!C10</f>
         <v>1.0863804981452041E-2</v>
       </c>
-      <c r="E15" s="185">
+      <c r="E15" s="68">
         <f>'Financial Data'!D18/'Financial Data'!D10</f>
         <v>4.0824261275272163E-3</v>
       </c>
-      <c r="F15" s="185">
+      <c r="F15" s="68">
         <f>'Financial Data'!E18/'Financial Data'!E10</f>
         <v>6.2637018477920449E-3</v>
       </c>
-      <c r="G15" s="185">
+      <c r="G15" s="68">
         <f>'Financial Data'!F18/'Financial Data'!F10</f>
         <v>9.0566037735849061E-3</v>
       </c>
-      <c r="H15" s="185">
+      <c r="H15" s="68">
         <f>'Financial Data'!G18/'Financial Data'!G10</f>
         <v>2.0355218519257635E-2</v>
       </c>
-      <c r="J15" s="204" t="s">
-        <v>121</v>
-      </c>
-      <c r="K15" s="205"/>
-      <c r="L15" s="205"/>
-      <c r="M15" s="206"/>
-      <c r="AA15" s="2" t="s">
+      <c r="O15" s="282"/>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="287"/>
+      <c r="Z15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AB15" s="233">
+      <c r="AA15" s="90">
         <v>5.9700000000000003E-2</v>
       </c>
-      <c r="AC15" s="233">
+      <c r="AB15" s="90">
         <v>9.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="16" spans="2:32" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="124" t="s">
+    <row r="16" spans="2:32" s="71" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="C16" s="182"/>
-      <c r="D16" s="185">
+      <c r="C16" s="250"/>
+      <c r="D16" s="68">
         <f>'Financial Data'!C18/'Financial Data'!C31</f>
         <v>1.5495086923658353E-2</v>
       </c>
-      <c r="E16" s="185">
+      <c r="E16" s="68">
         <f>'Financial Data'!D18/'Financial Data'!D31</f>
         <v>7.1186440677966098E-3</v>
       </c>
-      <c r="F16" s="185">
+      <c r="F16" s="68">
         <f>'Financial Data'!E18/'Financial Data'!E31</f>
         <v>1.1761246692149369E-2</v>
       </c>
-      <c r="G16" s="185">
+      <c r="G16" s="68">
         <f>'Financial Data'!F18/'Financial Data'!F31</f>
         <v>1.8090452261306532E-2</v>
       </c>
-      <c r="H16" s="185">
+      <c r="H16" s="68">
         <f>'Financial Data'!G18/'Financial Data'!G31</f>
         <v>4.4242029928432007E-2</v>
       </c>
-      <c r="J16" s="207"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="209"/>
-      <c r="AA16" s="2" t="s">
+      <c r="J16" s="155" t="s">
+        <v>160</v>
+      </c>
+      <c r="K16" s="156"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="289"/>
+      <c r="O16" s="282"/>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="287"/>
+      <c r="Z16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AB16" s="233">
+      <c r="AA16" s="90">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="AC16" s="233">
+      <c r="AB16" s="90">
         <v>2.0400000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:13" s="188" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="183" t="s">
+    <row r="17" spans="2:17" s="71" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="247" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="184"/>
-      <c r="D17" s="189">
+      <c r="C17" s="248"/>
+      <c r="D17" s="72">
         <f>'Financial Data'!C18/('Financial Data'!C36+'Financial Data'!C37)</f>
         <v>3.0619865571321882E-2</v>
       </c>
-      <c r="E17" s="189">
+      <c r="E17" s="72">
         <f>'Financial Data'!D18/('Financial Data'!D36+'Financial Data'!D37)</f>
         <v>1.5239477503628448E-2</v>
       </c>
-      <c r="F17" s="189">
+      <c r="F17" s="72">
         <f>'Financial Data'!E18/('Financial Data'!E36+'Financial Data'!E37)</f>
         <v>3.167062549485352E-2</v>
       </c>
-      <c r="G17" s="189">
+      <c r="G17" s="72">
         <f>'Financial Data'!F18/('Financial Data'!F36+'Financial Data'!F37)</f>
         <v>5.5342044581091467E-2</v>
       </c>
-      <c r="H17" s="189">
+      <c r="H17" s="72">
         <f>'Financial Data'!G18/('Financial Data'!G36+'Financial Data'!G37)</f>
         <v>0.14186369958275383</v>
       </c>
-      <c r="J17" s="207"/>
-      <c r="K17" s="208"/>
-      <c r="L17" s="208"/>
-      <c r="M17" s="209"/>
-    </row>
-    <row r="18" spans="2:13" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J18" s="207"/>
-      <c r="K18" s="208"/>
-      <c r="L18" s="208"/>
-      <c r="M18" s="209"/>
-    </row>
-    <row r="19" spans="2:13" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="98" t="s">
+      <c r="J17" s="274" t="s">
+        <v>103</v>
+      </c>
+      <c r="K17" s="275"/>
+      <c r="L17" s="275"/>
+      <c r="M17" s="276" t="s">
+        <v>156</v>
+      </c>
+      <c r="O17" s="284"/>
+      <c r="P17" s="285"/>
+      <c r="Q17" s="288"/>
+    </row>
+    <row r="18" spans="2:17" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="128" t="s">
+        <v>157</v>
+      </c>
+      <c r="K18" s="129"/>
+      <c r="L18" s="129"/>
+      <c r="M18" s="278">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="256" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="100"/>
-      <c r="J19" s="207"/>
-      <c r="K19" s="208"/>
-      <c r="L19" s="208"/>
-      <c r="M19" s="209"/>
-    </row>
-    <row r="20" spans="2:13" s="187" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="164" t="s">
+      <c r="C19" s="257"/>
+      <c r="D19" s="257"/>
+      <c r="E19" s="257"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="258"/>
+      <c r="J19" s="128" t="s">
+        <v>158</v>
+      </c>
+      <c r="K19" s="129"/>
+      <c r="L19" s="129"/>
+      <c r="M19" s="277">
+        <v>314.39999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="70" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="165"/>
-      <c r="D20" s="166" t="s">
+      <c r="C20" s="144"/>
+      <c r="D20" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E20" s="166" t="s">
+      <c r="E20" s="64" t="s">
         <v>52</v>
       </c>
-      <c r="F20" s="166" t="s">
+      <c r="F20" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="166" t="s">
+      <c r="G20" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="H20" s="167" t="s">
+      <c r="H20" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="J20" s="207"/>
-      <c r="K20" s="208"/>
-      <c r="L20" s="208"/>
-      <c r="M20" s="209"/>
-    </row>
-    <row r="21" spans="2:13" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="221" t="s">
+      <c r="J20" s="133" t="s">
+        <v>159</v>
+      </c>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="279">
+        <f>(M19-M18)/M18</f>
+        <v>-0.72053333333333336</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="71" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="259" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="219"/>
-      <c r="D21" s="220">
+      <c r="C21" s="260"/>
+      <c r="D21" s="83">
         <f>'Financial Data'!C43</f>
         <v>-354</v>
       </c>
-      <c r="E21" s="220">
+      <c r="E21" s="83">
         <f>'Financial Data'!D43</f>
         <v>-140</v>
       </c>
-      <c r="F21" s="220">
+      <c r="F21" s="83">
         <f>'Financial Data'!E43</f>
         <v>0</v>
       </c>
-      <c r="G21" s="220">
+      <c r="G21" s="83">
         <f>'Financial Data'!F43</f>
         <v>467</v>
       </c>
-      <c r="H21" s="222">
+      <c r="H21" s="84">
         <f>'Financial Data'!G43</f>
         <v>644</v>
       </c>
-      <c r="J21" s="207"/>
-      <c r="K21" s="208"/>
-      <c r="L21" s="208"/>
-      <c r="M21" s="209"/>
-    </row>
-    <row r="22" spans="2:13" s="188" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="124" t="s">
+    </row>
+    <row r="22" spans="2:17" s="71" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="249" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="182"/>
-      <c r="D22" s="133">
+      <c r="C22" s="250"/>
+      <c r="D22" s="45">
         <f>'Financial Data'!C48</f>
         <v>-448</v>
       </c>
-      <c r="E22" s="133">
+      <c r="E22" s="45">
         <f>'Financial Data'!D48</f>
         <v>-348</v>
       </c>
-      <c r="F22" s="133">
+      <c r="F22" s="45">
         <f>'Financial Data'!E48</f>
         <v>-110</v>
       </c>
-      <c r="G22" s="133">
+      <c r="G22" s="45">
         <f>'Financial Data'!F48</f>
         <v>339</v>
       </c>
-      <c r="H22" s="134">
+      <c r="H22" s="46">
         <f>'Financial Data'!G48</f>
         <v>493</v>
       </c>
-      <c r="J22" s="207"/>
-      <c r="K22" s="208"/>
-      <c r="L22" s="208"/>
-      <c r="M22" s="209"/>
-    </row>
-    <row r="23" spans="2:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="183" t="s">
+    </row>
+    <row r="23" spans="2:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="247" t="s">
         <v>122</v>
       </c>
-      <c r="C23" s="184"/>
-      <c r="D23" s="218">
+      <c r="C23" s="248"/>
+      <c r="D23" s="82">
         <f>'Financial Data'!C33/'Financial Data'!C38</f>
         <v>0.44286781179985063</v>
       </c>
-      <c r="E23" s="218">
+      <c r="E23" s="82">
         <f>'Financial Data'!D33/'Financial Data'!D38</f>
         <v>0.57910014513788099</v>
       </c>
-      <c r="F23" s="218">
+      <c r="F23" s="82">
         <f>'Financial Data'!E33/'Financial Data'!E38</f>
         <v>0.76722090261282661</v>
       </c>
-      <c r="G23" s="218">
+      <c r="G23" s="82">
         <f>'Financial Data'!F33/'Financial Data'!F38</f>
         <v>1.0153727901614142</v>
       </c>
-      <c r="H23" s="223">
+      <c r="H23" s="85">
         <f>'Financial Data'!G33/'Financial Data'!G38</f>
         <v>0.86091794158553547</v>
       </c>
-      <c r="J23" s="210"/>
-      <c r="K23" s="211"/>
-      <c r="L23" s="211"/>
-      <c r="M23" s="212"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M23"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B2:M3"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J8:K8"/>
+  <mergeCells count="39">
+    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q17"/>
+    <mergeCell ref="J20:L20"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="L12:M12"/>
@@ -9099,13 +10319,27 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="B4:M4"/>
+    <mergeCell ref="B2:M3"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J8:K8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9134,274 +10368,257 @@
   <sheetData>
     <row r="1" spans="2:17" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="85"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
+      <c r="Q2" s="94"/>
     </row>
     <row r="3" spans="2:17" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="88"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="97"/>
     </row>
     <row r="4" spans="2:17" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="264" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="239"/>
-      <c r="D4" s="239"/>
-      <c r="E4" s="239"/>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="239"/>
-      <c r="I4" s="239"/>
-      <c r="J4" s="239"/>
-      <c r="K4" s="239"/>
-      <c r="L4" s="239"/>
-      <c r="M4" s="239"/>
-      <c r="N4" s="239"/>
-      <c r="O4" s="239"/>
-      <c r="P4" s="239"/>
-      <c r="Q4" s="240"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
+      <c r="M4" s="265"/>
+      <c r="N4" s="265"/>
+      <c r="O4" s="265"/>
+      <c r="P4" s="265"/>
+      <c r="Q4" s="266"/>
     </row>
     <row r="5" spans="2:17" ht="19.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="146" t="s">
+      <c r="B5" s="227" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-      <c r="O5" s="147"/>
-      <c r="P5" s="147"/>
-      <c r="Q5" s="148"/>
+      <c r="C5" s="228"/>
+      <c r="D5" s="228"/>
+      <c r="E5" s="228"/>
+      <c r="F5" s="228"/>
+      <c r="G5" s="228"/>
+      <c r="H5" s="228"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="228"/>
+      <c r="K5" s="228"/>
+      <c r="L5" s="228"/>
+      <c r="M5" s="228"/>
+      <c r="N5" s="228"/>
+      <c r="O5" s="228"/>
+      <c r="P5" s="228"/>
+      <c r="Q5" s="229"/>
     </row>
     <row r="6" spans="2:17" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="224" t="s">
+    <row r="7" spans="2:17" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="224" t="s">
+      <c r="D7" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="229"/>
-      <c r="F7" s="225" t="s">
+      <c r="E7" s="87"/>
+      <c r="F7" s="269" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="226"/>
-      <c r="I7" s="225" t="s">
+      <c r="G7" s="270"/>
+      <c r="I7" s="269" t="s">
         <v>127</v>
       </c>
-      <c r="J7" s="226"/>
-      <c r="L7" s="225" t="s">
+      <c r="J7" s="270"/>
+      <c r="L7" s="269" t="s">
         <v>128</v>
       </c>
-      <c r="M7" s="226"/>
-    </row>
-    <row r="8" spans="2:17" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="241">
+      <c r="M7" s="270"/>
+      <c r="O7" s="261" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="262"/>
+      <c r="Q7" s="263"/>
+    </row>
+    <row r="8" spans="2:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="91">
         <f>'Financial Data'!G10</f>
         <v>10022</v>
       </c>
-      <c r="D8" s="241">
+      <c r="D8" s="91">
         <f>'Financial Data'!G18</f>
         <v>204</v>
       </c>
-      <c r="E8" s="230"/>
-      <c r="F8" s="227">
+      <c r="E8" s="88"/>
+      <c r="F8" s="267">
         <f>'Financial Analysis'!D9</f>
         <v>0.21571143169251283</v>
       </c>
-      <c r="G8" s="231"/>
-      <c r="I8" s="227">
+      <c r="G8" s="273"/>
+      <c r="I8" s="267">
         <f>'Financial Analysis'!H14</f>
         <v>7.5034923169028142E-2</v>
       </c>
-      <c r="J8" s="228"/>
-      <c r="L8" s="242">
+      <c r="J8" s="268"/>
+      <c r="L8" s="271">
         <f>'Financial Analysis'!H22</f>
         <v>493</v>
       </c>
-      <c r="M8" s="243"/>
-    </row>
-    <row r="10" spans="2:17" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:17" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O11" s="234" t="s">
-        <v>133</v>
-      </c>
-      <c r="P11" s="235"/>
-      <c r="Q11" s="236"/>
+      <c r="M8" s="272"/>
+      <c r="O8" s="290" t="s">
+        <v>135</v>
+      </c>
+      <c r="P8" s="291"/>
+      <c r="Q8" s="292"/>
+    </row>
+    <row r="9" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="293"/>
+      <c r="P9" s="294"/>
+      <c r="Q9" s="295"/>
+    </row>
+    <row r="10" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="293"/>
+      <c r="P10" s="294"/>
+      <c r="Q10" s="295"/>
+    </row>
+    <row r="11" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="293"/>
+      <c r="P11" s="294"/>
+      <c r="Q11" s="295"/>
     </row>
     <row r="12" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O12" s="237" t="s">
-        <v>135</v>
-      </c>
-      <c r="P12" s="246"/>
-      <c r="Q12" s="248"/>
+      <c r="O12" s="293"/>
+      <c r="P12" s="294"/>
+      <c r="Q12" s="295"/>
     </row>
     <row r="13" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O13" s="249"/>
-      <c r="P13" s="247"/>
-      <c r="Q13" s="250"/>
+      <c r="O13" s="293"/>
+      <c r="P13" s="294"/>
+      <c r="Q13" s="295"/>
     </row>
     <row r="14" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O14" s="249"/>
-      <c r="P14" s="247"/>
-      <c r="Q14" s="250"/>
+      <c r="O14" s="293"/>
+      <c r="P14" s="294"/>
+      <c r="Q14" s="295"/>
     </row>
     <row r="15" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O15" s="249"/>
-      <c r="P15" s="247"/>
-      <c r="Q15" s="250"/>
+      <c r="O15" s="293"/>
+      <c r="P15" s="294"/>
+      <c r="Q15" s="295"/>
     </row>
     <row r="16" spans="2:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O16" s="249"/>
-      <c r="P16" s="247"/>
-      <c r="Q16" s="250"/>
+      <c r="O16" s="293"/>
+      <c r="P16" s="294"/>
+      <c r="Q16" s="295"/>
     </row>
     <row r="17" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O17" s="249"/>
-      <c r="P17" s="247"/>
-      <c r="Q17" s="250"/>
+      <c r="O17" s="293"/>
+      <c r="P17" s="294"/>
+      <c r="Q17" s="295"/>
     </row>
     <row r="18" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O18" s="249"/>
-      <c r="P18" s="247"/>
-      <c r="Q18" s="250"/>
+      <c r="O18" s="293"/>
+      <c r="P18" s="294"/>
+      <c r="Q18" s="295"/>
     </row>
     <row r="19" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O19" s="249"/>
-      <c r="P19" s="247"/>
-      <c r="Q19" s="250"/>
+      <c r="O19" s="293"/>
+      <c r="P19" s="294"/>
+      <c r="Q19" s="295"/>
     </row>
     <row r="20" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O20" s="249"/>
-      <c r="P20" s="247"/>
-      <c r="Q20" s="250"/>
+      <c r="O20" s="293"/>
+      <c r="P20" s="294"/>
+      <c r="Q20" s="295"/>
     </row>
     <row r="21" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O21" s="249"/>
-      <c r="P21" s="247"/>
-      <c r="Q21" s="250"/>
+      <c r="O21" s="293"/>
+      <c r="P21" s="294"/>
+      <c r="Q21" s="295"/>
     </row>
     <row r="22" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O22" s="249"/>
-      <c r="P22" s="247"/>
-      <c r="Q22" s="250"/>
+      <c r="O22" s="293"/>
+      <c r="P22" s="294"/>
+      <c r="Q22" s="295"/>
     </row>
     <row r="23" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O23" s="249"/>
-      <c r="P23" s="247"/>
-      <c r="Q23" s="250"/>
+      <c r="O23" s="293"/>
+      <c r="P23" s="294"/>
+      <c r="Q23" s="295"/>
     </row>
     <row r="24" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O24" s="249"/>
-      <c r="P24" s="247"/>
-      <c r="Q24" s="250"/>
+      <c r="O24" s="293"/>
+      <c r="P24" s="294"/>
+      <c r="Q24" s="295"/>
     </row>
     <row r="25" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O25" s="249"/>
-      <c r="P25" s="247"/>
-      <c r="Q25" s="250"/>
+      <c r="O25" s="293"/>
+      <c r="P25" s="294"/>
+      <c r="Q25" s="295"/>
     </row>
     <row r="26" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O26" s="249"/>
-      <c r="P26" s="247"/>
-      <c r="Q26" s="250"/>
-    </row>
-    <row r="27" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O27" s="249"/>
-      <c r="P27" s="247"/>
-      <c r="Q27" s="250"/>
-    </row>
-    <row r="28" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O28" s="249"/>
-      <c r="P28" s="247"/>
-      <c r="Q28" s="250"/>
-    </row>
-    <row r="29" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O29" s="249"/>
-      <c r="P29" s="247"/>
-      <c r="Q29" s="250"/>
-    </row>
-    <row r="30" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O30" s="249"/>
-      <c r="P30" s="247"/>
-      <c r="Q30" s="250"/>
-    </row>
-    <row r="31" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O31" s="249"/>
-      <c r="P31" s="247"/>
-      <c r="Q31" s="250"/>
-    </row>
-    <row r="32" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O32" s="249"/>
-      <c r="P32" s="247"/>
-      <c r="Q32" s="250"/>
-    </row>
-    <row r="33" spans="15:17" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O33" s="249"/>
-      <c r="P33" s="247"/>
-      <c r="Q33" s="250"/>
-    </row>
-    <row r="34" spans="15:17" x14ac:dyDescent="0.25">
-      <c r="O34" s="249"/>
-      <c r="P34" s="247"/>
-      <c r="Q34" s="250"/>
-    </row>
-    <row r="35" spans="15:17" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O35" s="251"/>
-      <c r="P35" s="252"/>
-      <c r="Q35" s="253"/>
-    </row>
+      <c r="O26" s="293"/>
+      <c r="P26" s="294"/>
+      <c r="Q26" s="295"/>
+    </row>
+    <row r="27" spans="15:17" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O27" s="296"/>
+      <c r="P27" s="297"/>
+      <c r="Q27" s="298"/>
+    </row>
+    <row r="28" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="15:17" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="16.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="O7:Q7"/>
     <mergeCell ref="B2:Q3"/>
     <mergeCell ref="B4:Q4"/>
     <mergeCell ref="B5:Q5"/>
-    <mergeCell ref="O12:Q35"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="L8:M8"/>
     <mergeCell ref="L7:M7"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="F7:G7"/>
+    <mergeCell ref="O8:Q27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -9427,471 +10644,482 @@
   <sheetData>
     <row r="1" spans="2:18" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="85"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
+      <c r="Q2" s="93"/>
+      <c r="R2" s="94"/>
     </row>
     <row r="3" spans="2:18" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="87"/>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="87"/>
-      <c r="Q3" s="87"/>
-      <c r="R3" s="88"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="96"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="96"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="96"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="97"/>
     </row>
     <row r="4" spans="2:18" ht="19.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="149" t="s">
+      <c r="B4" s="98" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="150"/>
-      <c r="H4" s="150"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="150"/>
-      <c r="K4" s="150"/>
-      <c r="L4" s="150"/>
-      <c r="M4" s="150"/>
-      <c r="N4" s="150"/>
-      <c r="O4" s="150"/>
-      <c r="P4" s="150"/>
-      <c r="Q4" s="150"/>
-      <c r="R4" s="151"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="100"/>
     </row>
     <row r="5" spans="2:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:18" ht="21" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="146" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="L6" s="201" t="s">
+      <c r="C6" s="147"/>
+      <c r="L6" s="101" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="202"/>
-      <c r="N6" s="203"/>
-      <c r="P6" s="201" t="s">
+      <c r="M6" s="102"/>
+      <c r="N6" s="103"/>
+      <c r="P6" s="101" t="s">
         <v>148</v>
       </c>
-      <c r="Q6" s="202"/>
-      <c r="R6" s="203"/>
-    </row>
-    <row r="7" spans="2:18" s="114" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="254" t="s">
+      <c r="Q6" s="102"/>
+      <c r="R6" s="103"/>
+    </row>
+    <row r="7" spans="2:18" s="35" customFormat="1" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="148" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="255"/>
-      <c r="E7" s="274" t="s">
+      <c r="C7" s="149"/>
+      <c r="E7" s="113" t="s">
         <v>140</v>
       </c>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="276"/>
-      <c r="L7" s="204" t="s">
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="114"/>
+      <c r="L7" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="M7" s="205"/>
-      <c r="N7" s="206"/>
-      <c r="P7" s="204" t="s">
+      <c r="M7" s="105"/>
+      <c r="N7" s="106"/>
+      <c r="P7" s="104" t="s">
         <v>151</v>
       </c>
-      <c r="Q7" s="205"/>
-      <c r="R7" s="206"/>
+      <c r="Q7" s="105"/>
+      <c r="R7" s="106"/>
     </row>
     <row r="8" spans="2:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="256"/>
-      <c r="C8" s="257"/>
-      <c r="E8" s="105" t="s">
+      <c r="B8" s="150"/>
+      <c r="C8" s="151"/>
+      <c r="E8" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="F8" s="165" t="s">
+      <c r="F8" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165" t="s">
+      <c r="G8" s="144"/>
+      <c r="H8" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="I8" s="165"/>
-      <c r="J8" s="168"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="208"/>
-      <c r="N8" s="209"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="208"/>
-      <c r="R8" s="209"/>
+      <c r="I8" s="144"/>
+      <c r="J8" s="145"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="109"/>
+      <c r="P8" s="107"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="109"/>
     </row>
     <row r="9" spans="2:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="256"/>
-      <c r="C9" s="257"/>
-      <c r="E9" s="272" t="s">
+      <c r="B9" s="150"/>
+      <c r="C9" s="151"/>
+      <c r="E9" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="266" t="s">
+      <c r="F9" s="141" t="s">
         <v>142</v>
       </c>
-      <c r="G9" s="266"/>
-      <c r="H9" s="266" t="s">
+      <c r="G9" s="141"/>
+      <c r="H9" s="141" t="s">
         <v>143</v>
       </c>
-      <c r="I9" s="266"/>
-      <c r="J9" s="267"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="208"/>
-      <c r="N9" s="209"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="209"/>
+      <c r="I9" s="141"/>
+      <c r="J9" s="142"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="109"/>
+      <c r="P9" s="107"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="109"/>
     </row>
     <row r="10" spans="2:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="256"/>
-      <c r="C10" s="257"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
-      <c r="H10" s="268"/>
-      <c r="I10" s="268"/>
-      <c r="J10" s="269"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="208"/>
-      <c r="N10" s="209"/>
-      <c r="P10" s="207"/>
-      <c r="Q10" s="208"/>
-      <c r="R10" s="209"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="151"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="129"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="129"/>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="109"/>
+      <c r="P10" s="107"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="109"/>
     </row>
     <row r="11" spans="2:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="256"/>
-      <c r="C11" s="257"/>
-      <c r="E11" s="104" t="s">
+      <c r="B11" s="150"/>
+      <c r="C11" s="151"/>
+      <c r="E11" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="268" t="s">
+      <c r="F11" s="129" t="s">
         <v>155</v>
       </c>
-      <c r="G11" s="268"/>
-      <c r="H11" s="268" t="s">
+      <c r="G11" s="129"/>
+      <c r="H11" s="129" t="s">
         <v>144</v>
       </c>
-      <c r="I11" s="268"/>
-      <c r="J11" s="269"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="208"/>
-      <c r="N11" s="209"/>
-      <c r="P11" s="207"/>
-      <c r="Q11" s="208"/>
-      <c r="R11" s="209"/>
+      <c r="I11" s="129"/>
+      <c r="J11" s="130"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="109"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
     </row>
     <row r="12" spans="2:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="258"/>
-      <c r="C12" s="259"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="268"/>
-      <c r="G12" s="268"/>
-      <c r="H12" s="268"/>
-      <c r="I12" s="268"/>
-      <c r="J12" s="269"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="208"/>
-      <c r="N12" s="209"/>
-      <c r="P12" s="207"/>
-      <c r="Q12" s="208"/>
-      <c r="R12" s="209"/>
+      <c r="B12" s="152"/>
+      <c r="C12" s="153"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="129"/>
+      <c r="J12" s="130"/>
+      <c r="L12" s="107"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="109"/>
+      <c r="P12" s="107"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="109"/>
     </row>
     <row r="13" spans="2:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="104" t="s">
+      <c r="E13" s="128" t="s">
         <v>113</v>
       </c>
-      <c r="F13" s="268" t="s">
+      <c r="F13" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="G13" s="268"/>
-      <c r="H13" s="268" t="s">
+      <c r="G13" s="129"/>
+      <c r="H13" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="I13" s="268"/>
-      <c r="J13" s="269"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="208"/>
-      <c r="N13" s="209"/>
-      <c r="P13" s="207"/>
-      <c r="Q13" s="208"/>
-      <c r="R13" s="209"/>
+      <c r="I13" s="129"/>
+      <c r="J13" s="130"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="109"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="109"/>
     </row>
     <row r="14" spans="2:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="146" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="268"/>
-      <c r="G14" s="268"/>
-      <c r="H14" s="268"/>
-      <c r="I14" s="268"/>
-      <c r="J14" s="269"/>
-      <c r="L14" s="207"/>
-      <c r="M14" s="208"/>
-      <c r="N14" s="209"/>
-      <c r="P14" s="207"/>
-      <c r="Q14" s="208"/>
-      <c r="R14" s="209"/>
+      <c r="C14" s="147"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="130"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="109"/>
+      <c r="P14" s="107"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="109"/>
     </row>
     <row r="15" spans="2:18" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="260" t="s">
+      <c r="B15" s="134" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="261"/>
-      <c r="E15" s="104" t="s">
+      <c r="C15" s="135"/>
+      <c r="E15" s="128" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="268" t="s">
+      <c r="F15" s="129" t="s">
         <v>153</v>
       </c>
-      <c r="G15" s="268"/>
-      <c r="H15" s="268" t="s">
+      <c r="G15" s="129"/>
+      <c r="H15" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="I15" s="268"/>
-      <c r="J15" s="269"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="208"/>
-      <c r="N15" s="209"/>
-      <c r="P15" s="207"/>
-      <c r="Q15" s="208"/>
-      <c r="R15" s="209"/>
+      <c r="I15" s="129"/>
+      <c r="J15" s="130"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="109"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="109"/>
     </row>
     <row r="16" spans="2:18" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="262"/>
-      <c r="C16" s="263"/>
-      <c r="E16" s="273"/>
-      <c r="F16" s="270"/>
-      <c r="G16" s="270"/>
-      <c r="H16" s="270"/>
-      <c r="I16" s="270"/>
-      <c r="J16" s="271"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="208"/>
-      <c r="N16" s="209"/>
-      <c r="P16" s="207"/>
-      <c r="Q16" s="208"/>
-      <c r="R16" s="209"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="137"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="132"/>
+      <c r="L16" s="107"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="109"/>
+      <c r="P16" s="107"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="109"/>
     </row>
     <row r="17" spans="2:18" ht="34.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="264"/>
-      <c r="C17" s="265"/>
-      <c r="L17" s="210"/>
-      <c r="M17" s="211"/>
-      <c r="N17" s="212"/>
-      <c r="P17" s="210"/>
-      <c r="Q17" s="211"/>
-      <c r="R17" s="212"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="139"/>
+      <c r="L17" s="110"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="112"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="112"/>
     </row>
     <row r="18" spans="2:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="274" t="s">
+      <c r="B19" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="276"/>
-      <c r="D19" s="282" t="s">
+      <c r="C19" s="114"/>
+      <c r="D19" s="119" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="244"/>
-      <c r="F19" s="244"/>
-      <c r="G19" s="244"/>
-      <c r="H19" s="244"/>
-      <c r="I19" s="244"/>
-      <c r="J19" s="244"/>
-      <c r="K19" s="244"/>
-      <c r="L19" s="244"/>
-      <c r="M19" s="244"/>
-      <c r="N19" s="244"/>
-      <c r="O19" s="244"/>
-      <c r="P19" s="244"/>
-      <c r="Q19" s="244"/>
-      <c r="R19" s="128"/>
+      <c r="E19" s="120"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="120"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="120"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="121"/>
     </row>
     <row r="20" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="277"/>
-      <c r="C20" s="278"/>
-      <c r="D20" s="129"/>
-      <c r="E20" s="245"/>
-      <c r="F20" s="245"/>
-      <c r="G20" s="245"/>
-      <c r="H20" s="245"/>
-      <c r="I20" s="245"/>
-      <c r="J20" s="245"/>
-      <c r="K20" s="245"/>
-      <c r="L20" s="245"/>
-      <c r="M20" s="245"/>
-      <c r="N20" s="245"/>
-      <c r="O20" s="245"/>
-      <c r="P20" s="245"/>
-      <c r="Q20" s="245"/>
-      <c r="R20" s="130"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="124"/>
     </row>
     <row r="21" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="277"/>
-      <c r="C21" s="278"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="245"/>
-      <c r="G21" s="245"/>
-      <c r="H21" s="245"/>
-      <c r="I21" s="245"/>
-      <c r="J21" s="245"/>
-      <c r="K21" s="245"/>
-      <c r="L21" s="245"/>
-      <c r="M21" s="245"/>
-      <c r="N21" s="245"/>
-      <c r="O21" s="245"/>
-      <c r="P21" s="245"/>
-      <c r="Q21" s="245"/>
-      <c r="R21" s="130"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="123"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="124"/>
     </row>
     <row r="22" spans="2:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="277"/>
-      <c r="C22" s="278"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="245"/>
-      <c r="F22" s="245"/>
-      <c r="G22" s="245"/>
-      <c r="H22" s="245"/>
-      <c r="I22" s="245"/>
-      <c r="J22" s="245"/>
-      <c r="K22" s="245"/>
-      <c r="L22" s="245"/>
-      <c r="M22" s="245"/>
-      <c r="N22" s="245"/>
-      <c r="O22" s="245"/>
-      <c r="P22" s="245"/>
-      <c r="Q22" s="245"/>
-      <c r="R22" s="130"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="123"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="124"/>
     </row>
     <row r="23" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="277"/>
-      <c r="C23" s="278"/>
-      <c r="D23" s="129"/>
-      <c r="E23" s="245"/>
-      <c r="F23" s="245"/>
-      <c r="G23" s="245"/>
-      <c r="H23" s="245"/>
-      <c r="I23" s="245"/>
-      <c r="J23" s="245"/>
-      <c r="K23" s="245"/>
-      <c r="L23" s="245"/>
-      <c r="M23" s="245"/>
-      <c r="N23" s="245"/>
-      <c r="O23" s="245"/>
-      <c r="P23" s="245"/>
-      <c r="Q23" s="245"/>
-      <c r="R23" s="130"/>
+      <c r="B23" s="115"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="123"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="124"/>
     </row>
     <row r="24" spans="2:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="277"/>
-      <c r="C24" s="278"/>
-      <c r="D24" s="129"/>
-      <c r="E24" s="245"/>
-      <c r="F24" s="245"/>
-      <c r="G24" s="245"/>
-      <c r="H24" s="245"/>
-      <c r="I24" s="245"/>
-      <c r="J24" s="245"/>
-      <c r="K24" s="245"/>
-      <c r="L24" s="245"/>
-      <c r="M24" s="245"/>
-      <c r="N24" s="245"/>
-      <c r="O24" s="245"/>
-      <c r="P24" s="245"/>
-      <c r="Q24" s="245"/>
-      <c r="R24" s="130"/>
+      <c r="B24" s="115"/>
+      <c r="C24" s="116"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="123"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="123"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="123"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="124"/>
     </row>
     <row r="25" spans="2:18" ht="16.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="277"/>
-      <c r="C25" s="278"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="245"/>
-      <c r="F25" s="245"/>
-      <c r="G25" s="245"/>
-      <c r="H25" s="245"/>
-      <c r="I25" s="245"/>
-      <c r="J25" s="245"/>
-      <c r="K25" s="245"/>
-      <c r="L25" s="245"/>
-      <c r="M25" s="245"/>
-      <c r="N25" s="245"/>
-      <c r="O25" s="245"/>
-      <c r="P25" s="245"/>
-      <c r="Q25" s="245"/>
-      <c r="R25" s="130"/>
+      <c r="B25" s="115"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="123"/>
+      <c r="K25" s="123"/>
+      <c r="L25" s="123"/>
+      <c r="M25" s="123"/>
+      <c r="N25" s="123"/>
+      <c r="O25" s="123"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="123"/>
+      <c r="R25" s="124"/>
     </row>
     <row r="26" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="277"/>
-      <c r="C26" s="278"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
-      <c r="M26" s="245"/>
-      <c r="N26" s="245"/>
-      <c r="O26" s="245"/>
-      <c r="P26" s="245"/>
-      <c r="Q26" s="245"/>
-      <c r="R26" s="130"/>
+      <c r="B26" s="115"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="123"/>
+      <c r="K26" s="123"/>
+      <c r="L26" s="123"/>
+      <c r="M26" s="123"/>
+      <c r="N26" s="123"/>
+      <c r="O26" s="123"/>
+      <c r="P26" s="123"/>
+      <c r="Q26" s="123"/>
+      <c r="R26" s="124"/>
     </row>
     <row r="27" spans="2:18" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="279"/>
-      <c r="C27" s="280"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="281"/>
-      <c r="F27" s="281"/>
-      <c r="G27" s="281"/>
-      <c r="H27" s="281"/>
-      <c r="I27" s="281"/>
-      <c r="J27" s="281"/>
-      <c r="K27" s="281"/>
-      <c r="L27" s="281"/>
-      <c r="M27" s="281"/>
-      <c r="N27" s="281"/>
-      <c r="O27" s="281"/>
-      <c r="P27" s="281"/>
-      <c r="Q27" s="281"/>
-      <c r="R27" s="132"/>
+      <c r="B27" s="117"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="126"/>
+      <c r="G27" s="126"/>
+      <c r="H27" s="126"/>
+      <c r="I27" s="126"/>
+      <c r="J27" s="126"/>
+      <c r="K27" s="126"/>
+      <c r="L27" s="126"/>
+      <c r="M27" s="126"/>
+      <c r="N27" s="126"/>
+      <c r="O27" s="126"/>
+      <c r="P27" s="126"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="H13:J14"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="H11:J12"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="F8:G8"/>
     <mergeCell ref="B2:R3"/>
     <mergeCell ref="B4:R4"/>
     <mergeCell ref="P6:R6"/>
@@ -9908,17 +11136,6 @@
     <mergeCell ref="E7:J7"/>
     <mergeCell ref="H9:J10"/>
     <mergeCell ref="F9:G10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="H11:J12"/>
-    <mergeCell ref="F11:G12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H13:J14"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C12"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
